--- a/Deliverables/sprint-13/planning-documents.xlsx
+++ b/Deliverables/sprint-13/planning-documents.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="808">
   <si>
     <t>Project Name</t>
   </si>
@@ -681,19 +681,19 @@
     <t>PLEASE CREATE THE VELOCITY CHART ON A NEW TAB USING THE DATA FROM THIS TAB</t>
   </si>
   <si>
-    <t>Agent Config not persistant through text and voice prompts #99</t>
+    <t>Agent Config not persistant through text and voice prompts #99 [Bug]</t>
   </si>
   <si>
     <t>Agent/LLM Memory Safeguards #56</t>
   </si>
   <si>
-    <t>Voice input splits into multiple bubbles &amp; numbers/symbols are formatted wrong #102</t>
+    <t>Voice input splits into multiple bubbles &amp; numbers/symbols are formatted wrong #102 [Bug]</t>
   </si>
   <si>
     <t>Agent Routing Foundation #8</t>
   </si>
   <si>
-    <t>[PROD] Agent config not loaded correctly #100</t>
+    <t>[PROD] Agent config not loaded correctly #100 [Bug]</t>
   </si>
   <si>
     <t>Livekit - Session Limit #112</t>
@@ -711,7 +711,7 @@
     <t>Critical Action Confirmation #49</t>
   </si>
   <si>
-    <t>Microphone Mute interrupts Agent TTS output #101</t>
+    <t>Microphone Mute interrupts Agent TTS output #101 [Bug]</t>
   </si>
   <si>
     <t>Provider Model Dropdown #87</t>
@@ -738,19 +738,19 @@
     <t>Benchmarking Environment #86</t>
   </si>
   <si>
-    <t>Investigate high API usage rate #151</t>
-  </si>
-  <si>
-    <t>Voice detection does not terminate #153</t>
-  </si>
-  <si>
-    <t>Greeting message not showing up in the conversation history #164</t>
-  </si>
-  <si>
-    <t>Unplanned critical bug</t>
-  </si>
-  <si>
-    <t>LLM Streaming frontend integration #162</t>
+    <t>Investigate high API usage rate #151 [Bug]</t>
+  </si>
+  <si>
+    <t>Voice detection does not terminate #153 [Bug]</t>
+  </si>
+  <si>
+    <t>Greeting message not showing up in the conversation history #164 [Bug]</t>
+  </si>
+  <si>
+    <t>Unplanned bug</t>
+  </si>
+  <si>
+    <t>LLM Streaming frontend integration #162 [Bug]</t>
   </si>
   <si>
     <t>Component Benchmarking #68</t>
@@ -762,13 +762,13 @@
     <t>Self-Hosted LLM Inference on GCP #160</t>
   </si>
   <si>
-    <t>Email transcription issue #169</t>
-  </si>
-  <si>
-    <t>Agent Guadrails need to be added #168</t>
-  </si>
-  <si>
-    <t>fix: resolve Gemini intent routing and harden API security #177</t>
+    <t>Email transcription issue #169 [Bug]</t>
+  </si>
+  <si>
+    <t>Agent Guadrails need to be added #168 [Bug]</t>
+  </si>
+  <si>
+    <t>fix: resolve Gemini intent routing and harden API security #177 [Bug]</t>
   </si>
   <si>
     <t>Demo Video #187</t>
@@ -783,16 +783,16 @@
     <t xml:space="preserve">SBOM Automation &amp; Legal Notices UI #138 </t>
   </si>
   <si>
-    <t xml:space="preserve">ElevenLabs and Deepgram provider switching is unreliable #166 </t>
-  </si>
-  <si>
-    <t>Some LLM providers are not functioning reliably #197</t>
+    <t>ElevenLabs and Deepgram provider switching is unreliable #166  [Bug]</t>
+  </si>
+  <si>
+    <t>Some LLM providers are not functioning reliably #197 [Bug]</t>
   </si>
   <si>
     <t>Allow User to delete History Sessions #191</t>
   </si>
   <si>
-    <t>Consistent data extraction from the conversation and showing in history #159 &amp; 183</t>
+    <t>Consistent data extraction from the conversation and showing in history #159&amp;183 [Bug]</t>
   </si>
   <si>
     <t>Finalize user, (technical) design and build/deploy documentation #182</t>
@@ -804,22 +804,40 @@
     <t>Final Repository &amp; Readme Clean up #204</t>
   </si>
   <si>
-    <t>LiveKit "not configured" in Production #213</t>
+    <t>LiveKit "not configured" in Production #213 [Bug]</t>
   </si>
   <si>
     <t>Dynamic Critical Action Confirmation #143</t>
   </si>
   <si>
-    <t>Agent Transfer/Handoff not working #212</t>
-  </si>
-  <si>
-    <t>Grafana Backend Logs not displayed correctly #210</t>
-  </si>
-  <si>
-    <t>Custom Agents not selectable in Conditional Workflow #214</t>
-  </si>
-  <si>
-    <t>Canceled:</t>
+    <t>Interim Results in Final Release for IP</t>
+  </si>
+  <si>
+    <t>Agent Transfer/Handoff not working #212 [Bug]</t>
+  </si>
+  <si>
+    <t>Grafana Backend Logs not displayed correctly #210 [Bug]</t>
+  </si>
+  <si>
+    <t>Custom Agents not selectable in Conditional Workflow #214 [Bug]</t>
+  </si>
+  <si>
+    <t>Inconsistency with Save as new and Update buttons #235 [Bug]</t>
+  </si>
+  <si>
+    <t>Voice: transfer to a custom agent never completes (target agent never runs) #253 [Bug]</t>
+  </si>
+  <si>
+    <t>External API tools collect caller args in dispatch + stop fabricating answers on tool failure #245 [Bug]</t>
+  </si>
+  <si>
+    <t>External API tool config auto-detect template args, warn on misconfig, and test requests live #229 [Bug]</t>
+  </si>
+  <si>
+    <t>External API tools returning stale answers instead of live data #219 [Bug]</t>
+  </si>
+  <si>
+    <t>Canceled due to time constraints:</t>
   </si>
   <si>
     <t>Support Markdown formatting in Chat UI #165</t>
@@ -2564,7 +2582,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
@@ -2867,6 +2885,9 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -3249,8 +3270,8 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="943068295"/>
-        <c:axId val="1874832041"/>
+        <c:axId val="2122650614"/>
+        <c:axId val="1299751562"/>
       </c:barChart>
       <c:lineChart>
         <c:varyColors val="0"/>
@@ -3285,11 +3306,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="943068295"/>
-        <c:axId val="1874832041"/>
+        <c:axId val="2122650614"/>
+        <c:axId val="1299751562"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="943068295"/>
+        <c:axId val="2122650614"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3345,10 +3366,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1874832041"/>
+        <c:crossAx val="1299751562"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1874832041"/>
+        <c:axId val="1299751562"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3425,7 +3446,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="943068295"/>
+        <c:crossAx val="2122650614"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3578,8 +3599,8 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1553188822"/>
-        <c:axId val="436713329"/>
+        <c:axId val="1095476936"/>
+        <c:axId val="1494672521"/>
       </c:barChart>
       <c:lineChart>
         <c:varyColors val="0"/>
@@ -3614,11 +3635,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1553188822"/>
-        <c:axId val="436713329"/>
+        <c:axId val="1095476936"/>
+        <c:axId val="1494672521"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1553188822"/>
+        <c:axId val="1095476936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3674,10 +3695,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436713329"/>
+        <c:crossAx val="1494672521"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="436713329"/>
+        <c:axId val="1494672521"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3754,7 +3775,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1553188822"/>
+        <c:crossAx val="1095476936"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -3994,7 +4015,7 @@
   <tableColumns count="3">
     <tableColumn name="Sprint #" id="1"/>
     <tableColumn name="Story Points Realized" id="2"/>
-    <tableColumn name="Average Realized (25 SP/s)" id="3"/>
+    <tableColumn name="Average Realized (28 SP/s)" id="3"/>
   </tableColumns>
   <tableStyleInfo name="Calculations-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -4327,10 +4348,12 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="12.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.38"/>
-    <col customWidth="1" min="2" max="2" width="45.0"/>
-    <col customWidth="1" min="3" max="3" width="65.38"/>
-    <col customWidth="1" min="4" max="4" width="16.75"/>
-    <col customWidth="1" min="5" max="7" width="15.75"/>
+    <col customWidth="1" min="2" max="2" width="40.63"/>
+    <col customWidth="1" min="3" max="3" width="67.38"/>
+    <col customWidth="1" min="4" max="4" width="17.0"/>
+    <col customWidth="1" min="5" max="5" width="15.5"/>
+    <col customWidth="1" min="6" max="6" width="15.75"/>
+    <col customWidth="1" min="7" max="7" width="16.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4583,7 +4606,7 @@
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30">
-        <f>SUM(D74:D85)</f>
+        <f>SUM(D74:D90)</f>
         <v>45</v>
       </c>
       <c r="E15" s="30">
@@ -4591,8 +4614,8 @@
         <v>45</v>
       </c>
       <c r="F15" s="30">
-        <f>SUM(F74:F85)</f>
-        <v>0</v>
+        <f>SUM(F74:F90)</f>
+        <v>63</v>
       </c>
       <c r="G15" s="30">
         <f t="shared" si="3"/>
@@ -4817,7 +4840,7 @@
     <row r="31">
       <c r="A31" s="76"/>
       <c r="B31" s="54"/>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="28" t="s">
         <v>226</v>
       </c>
       <c r="D31" s="54">
@@ -4952,7 +4975,7 @@
     <row r="40">
       <c r="A40" s="30"/>
       <c r="B40" s="86"/>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="32" t="s">
         <v>226</v>
       </c>
       <c r="D40" s="86">
@@ -5026,7 +5049,7 @@
     <row r="45">
       <c r="A45" s="76"/>
       <c r="B45" s="54"/>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="28" t="s">
         <v>235</v>
       </c>
       <c r="D45" s="54">
@@ -5041,7 +5064,7 @@
     <row r="46">
       <c r="A46" s="66"/>
       <c r="B46" s="78"/>
-      <c r="C46" s="30" t="s">
+      <c r="C46" s="32" t="s">
         <v>236</v>
       </c>
       <c r="D46" s="30">
@@ -5059,7 +5082,7 @@
       <c r="C47" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="D47" s="81" t="s">
+      <c r="D47" s="87" t="s">
         <v>238</v>
       </c>
       <c r="E47" s="54"/>
@@ -5074,7 +5097,7 @@
       <c r="C48" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="D48" s="99" t="s">
+      <c r="D48" s="86" t="s">
         <v>238</v>
       </c>
       <c r="E48" s="30"/>
@@ -5154,7 +5177,7 @@
     <row r="54">
       <c r="A54" s="66"/>
       <c r="B54" s="78"/>
-      <c r="C54" s="30" t="s">
+      <c r="C54" s="32" t="s">
         <v>243</v>
       </c>
       <c r="D54" s="30">
@@ -5187,7 +5210,7 @@
       <c r="C56" s="99" t="s">
         <v>245</v>
       </c>
-      <c r="D56" s="99" t="s">
+      <c r="D56" s="86" t="s">
         <v>238</v>
       </c>
       <c r="E56" s="30"/>
@@ -5285,7 +5308,7 @@
     <row r="64">
       <c r="A64" s="66"/>
       <c r="B64" s="78"/>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="32" t="s">
         <v>250</v>
       </c>
       <c r="D64" s="30">
@@ -5300,7 +5323,7 @@
     <row r="65">
       <c r="A65" s="76"/>
       <c r="B65" s="54"/>
-      <c r="C65" s="54" t="s">
+      <c r="C65" s="28" t="s">
         <v>251</v>
       </c>
       <c r="D65" s="54">
@@ -5348,7 +5371,7 @@
       <c r="C68" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D68" s="99" t="s">
+      <c r="D68" s="86" t="s">
         <v>238</v>
       </c>
       <c r="E68" s="32"/>
@@ -5417,7 +5440,9 @@
         <v>3.0</v>
       </c>
       <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
+      <c r="F74" s="32">
+        <v>5.0</v>
+      </c>
       <c r="G74" s="30"/>
     </row>
     <row r="75">
@@ -5430,7 +5455,9 @@
         <v>3.0</v>
       </c>
       <c r="E75" s="54"/>
-      <c r="F75" s="69"/>
+      <c r="F75" s="81">
+        <v>3.0</v>
+      </c>
       <c r="G75" s="69"/>
     </row>
     <row r="76">
@@ -5443,20 +5470,24 @@
         <v>5.0</v>
       </c>
       <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
+      <c r="F76" s="32">
+        <v>5.0</v>
+      </c>
       <c r="G76" s="30"/>
     </row>
     <row r="77">
       <c r="A77" s="76"/>
       <c r="B77" s="54"/>
-      <c r="C77" s="54" t="s">
+      <c r="C77" s="28" t="s">
         <v>257</v>
       </c>
       <c r="D77" s="54">
         <v>2.0</v>
       </c>
       <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
+      <c r="F77" s="81">
+        <v>2.0</v>
+      </c>
       <c r="G77" s="69"/>
     </row>
     <row r="78">
@@ -5469,7 +5500,9 @@
         <v>3.0</v>
       </c>
       <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
+      <c r="F78" s="32">
+        <v>3.0</v>
+      </c>
       <c r="G78" s="30"/>
     </row>
     <row r="79">
@@ -5482,7 +5515,9 @@
         <v>5.0</v>
       </c>
       <c r="E79" s="69"/>
-      <c r="F79" s="69"/>
+      <c r="F79" s="81">
+        <v>5.0</v>
+      </c>
       <c r="G79" s="69"/>
     </row>
     <row r="80">
@@ -5495,33 +5530,41 @@
         <v>8.0</v>
       </c>
       <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30"/>
+      <c r="F80" s="82" t="s">
+        <v>190</v>
+      </c>
+      <c r="G80" s="101" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="80"/>
       <c r="B81" s="54"/>
-      <c r="C81" s="54" t="s">
-        <v>259</v>
+      <c r="C81" s="28" t="s">
+        <v>260</v>
       </c>
       <c r="D81" s="54">
         <v>5.0</v>
       </c>
       <c r="E81" s="54"/>
-      <c r="F81" s="54"/>
+      <c r="F81" s="28">
+        <v>5.0</v>
+      </c>
       <c r="G81" s="54"/>
     </row>
     <row r="82">
       <c r="A82" s="66"/>
       <c r="B82" s="30"/>
-      <c r="C82" s="30" t="s">
-        <v>260</v>
+      <c r="C82" s="32" t="s">
+        <v>261</v>
       </c>
       <c r="D82" s="32">
         <v>3.0</v>
       </c>
       <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
+      <c r="F82" s="32">
+        <v>3.0</v>
+      </c>
       <c r="G82" s="30"/>
     </row>
     <row r="83">
@@ -5534,65 +5577,99 @@
         <v>5.0</v>
       </c>
       <c r="E83" s="54"/>
-      <c r="F83" s="54"/>
+      <c r="F83" s="28">
+        <v>5.0</v>
+      </c>
       <c r="G83" s="54"/>
     </row>
     <row r="84">
       <c r="A84" s="66"/>
       <c r="B84" s="30"/>
-      <c r="C84" s="30" t="s">
-        <v>261</v>
+      <c r="C84" s="32" t="s">
+        <v>262</v>
       </c>
       <c r="D84" s="32">
         <v>3.0</v>
       </c>
       <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
+      <c r="F84" s="32">
+        <v>3.0</v>
+      </c>
       <c r="G84" s="30"/>
     </row>
     <row r="85">
       <c r="A85" s="80"/>
       <c r="B85" s="54"/>
-      <c r="C85" s="28"/>
-      <c r="D85" s="81"/>
+      <c r="C85" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="D85" s="87" t="s">
+        <v>238</v>
+      </c>
       <c r="E85" s="54"/>
-      <c r="F85" s="54"/>
+      <c r="F85" s="28">
+        <v>5.0</v>
+      </c>
       <c r="G85" s="54"/>
     </row>
     <row r="86">
       <c r="A86" s="66"/>
       <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="32"/>
+      <c r="C86" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" s="86" t="s">
+        <v>238</v>
+      </c>
       <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
+      <c r="F86" s="32">
+        <v>8.0</v>
+      </c>
       <c r="G86" s="30"/>
     </row>
     <row r="87">
       <c r="A87" s="80"/>
       <c r="B87" s="54"/>
-      <c r="C87" s="54"/>
-      <c r="D87" s="54"/>
+      <c r="C87" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="D87" s="87" t="s">
+        <v>238</v>
+      </c>
       <c r="E87" s="54"/>
-      <c r="F87" s="54"/>
+      <c r="F87" s="28">
+        <v>3.0</v>
+      </c>
       <c r="G87" s="54"/>
     </row>
     <row r="88">
       <c r="A88" s="66"/>
       <c r="B88" s="30"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="32"/>
+      <c r="C88" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D88" s="86" t="s">
+        <v>238</v>
+      </c>
       <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
+      <c r="F88" s="32">
+        <v>5.0</v>
+      </c>
       <c r="G88" s="30"/>
     </row>
     <row r="89">
       <c r="A89" s="80"/>
       <c r="B89" s="54"/>
-      <c r="C89" s="54"/>
-      <c r="D89" s="54"/>
+      <c r="C89" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D89" s="87" t="s">
+        <v>238</v>
+      </c>
       <c r="E89" s="54"/>
-      <c r="F89" s="54"/>
+      <c r="F89" s="28">
+        <v>3.0</v>
+      </c>
       <c r="G89" s="54"/>
     </row>
     <row r="90">
@@ -5617,7 +5694,6 @@
       <c r="A92" s="80"/>
       <c r="B92" s="54"/>
       <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
       <c r="E92" s="54"/>
       <c r="F92" s="54"/>
       <c r="G92" s="54"/>
@@ -5634,9 +5710,6 @@
     <row r="94">
       <c r="A94" s="80"/>
       <c r="B94" s="54"/>
-      <c r="C94" s="28" t="s">
-        <v>262</v>
-      </c>
       <c r="D94" s="54"/>
       <c r="E94" s="54"/>
       <c r="F94" s="54"/>
@@ -5645,9 +5718,7 @@
     <row r="95">
       <c r="A95" s="80"/>
       <c r="B95" s="54"/>
-      <c r="C95" s="54" t="s">
-        <v>263</v>
-      </c>
+      <c r="C95" s="54"/>
       <c r="D95" s="54"/>
       <c r="E95" s="54"/>
       <c r="F95" s="54"/>
@@ -5656,8 +5727,8 @@
     <row r="96">
       <c r="A96" s="80"/>
       <c r="B96" s="54"/>
-      <c r="C96" s="101" t="s">
-        <v>264</v>
+      <c r="C96" s="31" t="s">
+        <v>268</v>
       </c>
       <c r="D96" s="54"/>
       <c r="E96" s="54"/>
@@ -5667,7 +5738,9 @@
     <row r="97">
       <c r="A97" s="80"/>
       <c r="B97" s="54"/>
-      <c r="C97" s="54"/>
+      <c r="C97" s="30" t="s">
+        <v>240</v>
+      </c>
       <c r="D97" s="54"/>
       <c r="E97" s="54"/>
       <c r="F97" s="54"/>
@@ -5676,8 +5749,8 @@
     <row r="98">
       <c r="A98" s="80"/>
       <c r="B98" s="54"/>
-      <c r="C98" s="102" t="s">
-        <v>212</v>
+      <c r="C98" s="54" t="s">
+        <v>269</v>
       </c>
       <c r="D98" s="54"/>
       <c r="E98" s="54"/>
@@ -5687,7 +5760,9 @@
     <row r="99">
       <c r="A99" s="80"/>
       <c r="B99" s="54"/>
-      <c r="C99" s="54"/>
+      <c r="C99" s="102" t="s">
+        <v>270</v>
+      </c>
       <c r="D99" s="54"/>
       <c r="E99" s="54"/>
       <c r="F99" s="54"/>
@@ -5696,7 +5771,6 @@
     <row r="100">
       <c r="A100" s="80"/>
       <c r="B100" s="54"/>
-      <c r="C100" s="54"/>
       <c r="D100" s="54"/>
       <c r="E100" s="54"/>
       <c r="F100" s="54"/>
@@ -5714,7 +5788,9 @@
     <row r="102">
       <c r="A102" s="80"/>
       <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
+      <c r="C102" s="103" t="s">
+        <v>212</v>
+      </c>
       <c r="D102" s="54"/>
       <c r="E102" s="54"/>
       <c r="F102" s="54"/>
@@ -5790,23 +5866,23 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C1" s="49" t="s">
-        <v>266</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>267</v>
+        <v>272</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -5814,7 +5890,7 @@
     <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -5822,7 +5898,7 @@
     <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -5830,7 +5906,7 @@
     <row r="5">
       <c r="A5" s="3"/>
       <c r="B5" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -5839,7 +5915,7 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -5847,7 +5923,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -5855,7 +5931,7 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
@@ -5863,7 +5939,7 @@
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5947,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
@@ -5879,7 +5955,7 @@
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5887,7 +5963,7 @@
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13">
@@ -5895,7 +5971,7 @@
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14">
@@ -5903,7 +5979,7 @@
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15">
@@ -5911,7 +5987,7 @@
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16">
@@ -5919,7 +5995,7 @@
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -5927,7 +6003,7 @@
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18">
@@ -5935,7 +6011,7 @@
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19">
@@ -5971,15 +6047,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>17</v>
@@ -5987,31 +6063,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -6092,6 +6168,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="12.75"/>
   <cols>
@@ -6108,19 +6185,19 @@
         <v>69</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2">
@@ -6128,16 +6205,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E2" s="35" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3">
@@ -6145,16 +6222,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4">
@@ -6162,16 +6239,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -6179,16 +6256,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
@@ -6196,16 +6273,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7">
@@ -6213,16 +6290,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C7" s="35" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7" s="35" t="s">
         <v>312</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="8">
@@ -6230,16 +6307,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -6247,16 +6324,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -6264,16 +6341,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -6281,16 +6358,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D11" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E11" s="35" t="s">
         <v>322</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="12">
@@ -6298,16 +6375,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
@@ -6315,16 +6392,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14">
@@ -6332,16 +6409,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15">
@@ -6349,34 +6426,34 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="J15" s="105"/>
+        <v>312</v>
+      </c>
+      <c r="J15" s="106"/>
     </row>
     <row r="16">
       <c r="A16" s="35">
         <v>15.0</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17">
@@ -6384,16 +6461,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18">
@@ -6401,16 +6478,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19">
@@ -6418,16 +6495,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20">
@@ -6435,16 +6512,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="D20" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="D20" s="35" t="s">
-        <v>330</v>
-      </c>
       <c r="E20" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21">
@@ -6452,16 +6529,16 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22">
@@ -6469,16 +6546,16 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23">
@@ -6486,16 +6563,16 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24">
@@ -6503,16 +6580,16 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25">
@@ -6520,16 +6597,16 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="26">
@@ -6537,16 +6614,16 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27">
@@ -6554,16 +6631,16 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28">
@@ -6571,16 +6648,16 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29">
@@ -6588,16 +6665,16 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30">
@@ -6605,16 +6682,16 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31">
@@ -6622,16 +6699,16 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32">
@@ -6639,16 +6716,16 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33">
@@ -6656,16 +6733,16 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34">
@@ -6673,16 +6750,16 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D34" s="35" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35">
@@ -6690,16 +6767,16 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36">
@@ -6707,16 +6784,16 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37">
@@ -6724,16 +6801,16 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38">
@@ -6741,16 +6818,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39">
@@ -6758,16 +6835,16 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40">
@@ -6775,16 +6852,16 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E40" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41">
@@ -6792,16 +6869,16 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E41" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42">
@@ -6809,16 +6886,16 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E42" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43">
@@ -6826,16 +6903,16 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E43" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44">
@@ -6843,16 +6920,16 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45">
@@ -6860,16 +6937,16 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46">
@@ -6877,16 +6954,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47">
@@ -6894,16 +6971,16 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48">
@@ -6911,16 +6988,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E48" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49">
@@ -6928,16 +7005,16 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E49" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50">
@@ -6945,16 +7022,16 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C50" s="35" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E50" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51">
@@ -6962,16 +7039,16 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C51" s="35" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E51" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52">
@@ -6979,16 +7056,16 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E52" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53">
@@ -6996,16 +7073,16 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E53" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54">
@@ -7013,16 +7090,16 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="55">
@@ -7030,16 +7107,16 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E55" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="56">
@@ -7047,16 +7124,16 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="57">
@@ -7064,16 +7141,16 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="58">
@@ -7081,16 +7158,16 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E58" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59">
@@ -7098,16 +7175,16 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D59" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60">
@@ -7115,16 +7192,16 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61">
@@ -7132,16 +7209,16 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C61" s="35" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E61" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62">
@@ -7149,16 +7226,16 @@
         <v>61.0</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63">
@@ -7166,16 +7243,16 @@
         <v>62.0</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E63" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64">
@@ -7183,16 +7260,16 @@
         <v>63.0</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65">
@@ -7200,16 +7277,16 @@
         <v>64.0</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E65" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66">
@@ -7217,16 +7294,16 @@
         <v>65.0</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="67">
@@ -7234,16 +7311,16 @@
         <v>66.0</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D67" s="35" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E67" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68">
@@ -7251,16 +7328,16 @@
         <v>67.0</v>
       </c>
       <c r="B68" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D68" s="35" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69">
@@ -7268,16 +7345,16 @@
         <v>68.0</v>
       </c>
       <c r="B69" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C69" s="35" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E69" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="70">
@@ -7285,16 +7362,16 @@
         <v>69.0</v>
       </c>
       <c r="B70" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D70" s="35" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71">
@@ -7302,16 +7379,16 @@
         <v>70.0</v>
       </c>
       <c r="B71" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D71" s="35" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E71" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="72">
@@ -7319,16 +7396,16 @@
         <v>71.0</v>
       </c>
       <c r="B72" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D72" s="35" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="73">
@@ -7336,16 +7413,16 @@
         <v>72.0</v>
       </c>
       <c r="B73" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D73" s="35" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E73" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="74">
@@ -7353,16 +7430,16 @@
         <v>73.0</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75">
@@ -7370,16 +7447,16 @@
         <v>74.0</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="76">
@@ -7387,16 +7464,16 @@
         <v>75.0</v>
       </c>
       <c r="B76" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D76" s="35" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E76" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="77">
@@ -7404,16 +7481,16 @@
         <v>76.0</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D77" s="35" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78">
@@ -7421,16 +7498,16 @@
         <v>77.0</v>
       </c>
       <c r="B78" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D78" s="35" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E78" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="79">
@@ -7438,16 +7515,16 @@
         <v>78.0</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E79" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80">
@@ -7455,16 +7532,16 @@
         <v>79.0</v>
       </c>
       <c r="B80" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E80" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="81">
@@ -7472,16 +7549,16 @@
         <v>80.0</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C81" s="35" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D81" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E81" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82">
@@ -7489,16 +7566,16 @@
         <v>81.0</v>
       </c>
       <c r="B82" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C82" s="35" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D82" s="35" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E82" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83">
@@ -7506,16 +7583,16 @@
         <v>82.0</v>
       </c>
       <c r="B83" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E83" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84">
@@ -7523,16 +7600,16 @@
         <v>83.0</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C84" s="35" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E84" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="85">
@@ -7540,16 +7617,16 @@
         <v>84.0</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D85" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86">
@@ -7557,16 +7634,16 @@
         <v>85.0</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C86" s="35" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D86" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E86" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87">
@@ -7574,16 +7651,16 @@
         <v>86.0</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C87" s="35" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E87" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="88">
@@ -7591,16 +7668,16 @@
         <v>87.0</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C88" s="35" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D88" s="35" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="89">
@@ -7608,16 +7685,16 @@
         <v>88.0</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C89" s="35" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D89" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="90">
@@ -7625,16 +7702,16 @@
         <v>89.0</v>
       </c>
       <c r="B90" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C90" s="35" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D90" s="35" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="91">
@@ -7642,16 +7719,16 @@
         <v>90.0</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C91" s="35" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D91" s="35" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E91" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="92">
@@ -7659,16 +7736,16 @@
         <v>91.0</v>
       </c>
       <c r="B92" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C92" s="35" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D92" s="35" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E92" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="93">
@@ -7676,16 +7753,16 @@
         <v>92.0</v>
       </c>
       <c r="B93" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C93" s="35" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D93" s="35" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E93" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94">
@@ -7693,16 +7770,16 @@
         <v>93.0</v>
       </c>
       <c r="B94" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C94" s="35" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D94" s="35" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E94" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95">
@@ -7710,16 +7787,16 @@
         <v>94.0</v>
       </c>
       <c r="B95" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C95" s="35" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D95" s="35" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="96">
@@ -7727,16 +7804,16 @@
         <v>95.0</v>
       </c>
       <c r="B96" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C96" s="35" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D96" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="97">
@@ -7744,16 +7821,16 @@
         <v>96.0</v>
       </c>
       <c r="B97" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C97" s="35" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D97" s="35" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="98">
@@ -7761,16 +7838,16 @@
         <v>97.0</v>
       </c>
       <c r="B98" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="99">
@@ -7778,16 +7855,16 @@
         <v>98.0</v>
       </c>
       <c r="B99" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C99" s="35" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E99" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100">
@@ -7795,16 +7872,16 @@
         <v>99.0</v>
       </c>
       <c r="B100" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C100" s="35" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D100" s="35" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E100" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="101">
@@ -7812,16 +7889,16 @@
         <v>100.0</v>
       </c>
       <c r="B101" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C101" s="35" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D101" s="35" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E101" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102">
@@ -7829,16 +7906,16 @@
         <v>101.0</v>
       </c>
       <c r="B102" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C102" s="35" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D102" s="35" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E102" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="103">
@@ -7846,16 +7923,16 @@
         <v>102.0</v>
       </c>
       <c r="B103" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C103" s="35" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D103" s="35" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E103" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="104">
@@ -7863,16 +7940,16 @@
         <v>103.0</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D104" s="35" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E104" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105">
@@ -7880,16 +7957,16 @@
         <v>104.0</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C105" s="35" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D105" s="35" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E105" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106">
@@ -7897,16 +7974,16 @@
         <v>105.0</v>
       </c>
       <c r="B106" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C106" s="35" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D106" s="35" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E106" s="35" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="107">
@@ -7914,16 +7991,16 @@
         <v>106.0</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C107" s="35" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E107" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="108">
@@ -7931,16 +8008,16 @@
         <v>107.0</v>
       </c>
       <c r="B108" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C108" s="35" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D108" s="35" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E108" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="109">
@@ -7948,16 +8025,16 @@
         <v>108.0</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C109" s="35" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D109" s="35" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="110">
@@ -7965,16 +8042,16 @@
         <v>109.0</v>
       </c>
       <c r="B110" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C110" s="35" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D110" s="35" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111">
@@ -7982,16 +8059,16 @@
         <v>110.0</v>
       </c>
       <c r="B111" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C111" s="35" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E111" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112">
@@ -7999,16 +8076,16 @@
         <v>111.0</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C112" s="35" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E112" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113">
@@ -8016,16 +8093,16 @@
         <v>112.0</v>
       </c>
       <c r="B113" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C113" s="35" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D113" s="35" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E113" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114">
@@ -8033,16 +8110,16 @@
         <v>113.0</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C114" s="35" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D114" s="35" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E114" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="115">
@@ -8050,16 +8127,16 @@
         <v>114.0</v>
       </c>
       <c r="B115" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C115" s="35" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E115" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="116">
@@ -8067,16 +8144,16 @@
         <v>115.0</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C116" s="35" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E116" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="117">
@@ -8084,16 +8161,16 @@
         <v>116.0</v>
       </c>
       <c r="B117" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C117" s="35" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E117" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="118">
@@ -8101,16 +8178,16 @@
         <v>117.0</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C118" s="35" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D118" s="35" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E118" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119">
@@ -8118,16 +8195,16 @@
         <v>118.0</v>
       </c>
       <c r="B119" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120">
@@ -8135,16 +8212,16 @@
         <v>119.0</v>
       </c>
       <c r="B120" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C120" s="35" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D120" s="35" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E120" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="121">
@@ -8152,16 +8229,16 @@
         <v>120.0</v>
       </c>
       <c r="B121" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D121" s="35" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="E121" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122">
@@ -8169,16 +8246,16 @@
         <v>121.0</v>
       </c>
       <c r="B122" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C122" s="35" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D122" s="35" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E122" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="123">
@@ -8186,16 +8263,16 @@
         <v>122.0</v>
       </c>
       <c r="B123" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C123" s="35" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D123" s="35" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E123" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="124">
@@ -8203,16 +8280,16 @@
         <v>123.0</v>
       </c>
       <c r="B124" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C124" s="35" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D124" s="35" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E124" s="35" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125">
@@ -8220,16 +8297,16 @@
         <v>124.0</v>
       </c>
       <c r="B125" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C125" s="35" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D125" s="35" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E125" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="126">
@@ -8237,16 +8314,16 @@
         <v>125.0</v>
       </c>
       <c r="B126" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C126" s="35" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D126" s="35" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E126" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="127">
@@ -8254,16 +8331,16 @@
         <v>126.0</v>
       </c>
       <c r="B127" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C127" s="35" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D127" s="35" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E127" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="128">
@@ -8271,16 +8348,16 @@
         <v>127.0</v>
       </c>
       <c r="B128" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C128" s="35" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D128" s="35" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E128" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129">
@@ -8288,16 +8365,16 @@
         <v>128.0</v>
       </c>
       <c r="B129" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C129" s="35" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E129" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="130">
@@ -8305,16 +8382,16 @@
         <v>129.0</v>
       </c>
       <c r="B130" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C130" s="35" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D130" s="35" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E130" s="35" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="131">
@@ -8322,16 +8399,16 @@
         <v>130.0</v>
       </c>
       <c r="B131" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C131" s="35" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E131" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="132">
@@ -8339,16 +8416,16 @@
         <v>131.0</v>
       </c>
       <c r="B132" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C132" s="35" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E132" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="133">
@@ -8356,16 +8433,16 @@
         <v>132.0</v>
       </c>
       <c r="B133" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C133" s="35" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E133" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="134">
@@ -8373,16 +8450,16 @@
         <v>133.0</v>
       </c>
       <c r="B134" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C134" s="35" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E134" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="135">
@@ -8390,16 +8467,16 @@
         <v>134.0</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C135" s="35" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E135" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="136">
@@ -8407,16 +8484,16 @@
         <v>135.0</v>
       </c>
       <c r="B136" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C136" s="35" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E136" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="137">
@@ -8424,16 +8501,16 @@
         <v>136.0</v>
       </c>
       <c r="B137" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C137" s="35" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E137" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="138">
@@ -8441,16 +8518,16 @@
         <v>137.0</v>
       </c>
       <c r="B138" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C138" s="35" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E138" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="139">
@@ -8458,16 +8535,16 @@
         <v>138.0</v>
       </c>
       <c r="B139" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C139" s="35" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E139" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="140">
@@ -8475,16 +8552,16 @@
         <v>139.0</v>
       </c>
       <c r="B140" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C140" s="35" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="141">
@@ -8492,16 +8569,16 @@
         <v>140.0</v>
       </c>
       <c r="B141" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C141" s="35" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D141" s="35" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E141" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="142">
@@ -8509,16 +8586,16 @@
         <v>141.0</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C142" s="35" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D142" s="35" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E142" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="143">
@@ -8526,16 +8603,16 @@
         <v>142.0</v>
       </c>
       <c r="B143" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C143" s="35" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D143" s="35" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E143" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144">
@@ -8543,16 +8620,16 @@
         <v>143.0</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C144" s="35" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E144" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="145">
@@ -8560,16 +8637,16 @@
         <v>144.0</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C145" s="35" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D145" s="35" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E145" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="146">
@@ -8577,16 +8654,16 @@
         <v>145.0</v>
       </c>
       <c r="B146" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C146" s="35" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D146" s="35" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="E146" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="147">
@@ -8594,16 +8671,16 @@
         <v>146.0</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C147" s="35" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E147" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="148">
@@ -8611,16 +8688,16 @@
         <v>147.0</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C148" s="35" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E148" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="149">
@@ -8628,16 +8705,16 @@
         <v>148.0</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C149" s="35" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="D149" s="35" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E149" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="150">
@@ -8645,16 +8722,16 @@
         <v>149.0</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E150" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="151">
@@ -8662,16 +8739,16 @@
         <v>150.0</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C151" s="35" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E151" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="152">
@@ -8679,16 +8756,16 @@
         <v>151.0</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="D152" s="35" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E152" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="153">
@@ -8696,16 +8773,16 @@
         <v>152.0</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C153" s="35" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D153" s="35" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E153" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="154">
@@ -8713,16 +8790,16 @@
         <v>153.0</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C154" s="35" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E154" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="155">
@@ -8730,16 +8807,16 @@
         <v>154.0</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C155" s="35" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E155" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="156">
@@ -8747,16 +8824,16 @@
         <v>155.0</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="E156" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="157">
@@ -8764,16 +8841,16 @@
         <v>156.0</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C157" s="35" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E157" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="158">
@@ -8781,16 +8858,16 @@
         <v>157.0</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D158" s="35" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E158" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="159">
@@ -8798,16 +8875,16 @@
         <v>158.0</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C159" s="35" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E159" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="160">
@@ -8815,16 +8892,16 @@
         <v>159.0</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E160" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="161">
@@ -8832,16 +8909,16 @@
         <v>160.0</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E161" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="162">
@@ -8849,16 +8926,16 @@
         <v>161.0</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="E162" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="163">
@@ -8866,16 +8943,16 @@
         <v>162.0</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C163" s="35" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="D163" s="35" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="E163" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="164">
@@ -8883,16 +8960,16 @@
         <v>163.0</v>
       </c>
       <c r="B164" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C164" s="35" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D164" s="35" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E164" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="165">
@@ -8900,16 +8977,16 @@
         <v>164.0</v>
       </c>
       <c r="B165" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C165" s="35" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D165" s="35" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E165" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="166">
@@ -8917,16 +8994,16 @@
         <v>165.0</v>
       </c>
       <c r="B166" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D166" s="35" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="E166" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="167">
@@ -8934,16 +9011,16 @@
         <v>166.0</v>
       </c>
       <c r="B167" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C167" s="35" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E167" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="168">
@@ -8951,16 +9028,16 @@
         <v>167.0</v>
       </c>
       <c r="B168" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C168" s="35" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E168" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="169">
@@ -8968,16 +9045,16 @@
         <v>168.0</v>
       </c>
       <c r="B169" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C169" s="35" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E169" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="170">
@@ -8985,16 +9062,16 @@
         <v>169.0</v>
       </c>
       <c r="B170" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C170" s="35" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D170" s="35" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E170" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="171">
@@ -9002,16 +9079,16 @@
         <v>170.0</v>
       </c>
       <c r="B171" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C171" s="35" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D171" s="35">
         <v>3.13</v>
       </c>
       <c r="E171" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="172">
@@ -9019,16 +9096,16 @@
         <v>171.0</v>
       </c>
       <c r="B172" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C172" s="35" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="E172" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="173">
@@ -9036,16 +9113,16 @@
         <v>172.0</v>
       </c>
       <c r="B173" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C173" s="35" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="E173" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174">
@@ -9053,16 +9130,16 @@
         <v>173.0</v>
       </c>
       <c r="B174" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C174" s="35" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="E174" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="175">
@@ -9070,16 +9147,16 @@
         <v>174.0</v>
       </c>
       <c r="B175" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C175" s="35" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E175" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="176">
@@ -9087,16 +9164,16 @@
         <v>175.0</v>
       </c>
       <c r="B176" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C176" s="35" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E176" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="177">
@@ -9104,16 +9181,16 @@
         <v>176.0</v>
       </c>
       <c r="B177" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C177" s="35" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D177" s="35" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E177" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="178">
@@ -9121,16 +9198,16 @@
         <v>177.0</v>
       </c>
       <c r="B178" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C178" s="35" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D178" s="35" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="E178" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="179">
@@ -9138,16 +9215,16 @@
         <v>178.0</v>
       </c>
       <c r="B179" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C179" s="35" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D179" s="35" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E179" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="180">
@@ -9155,16 +9232,16 @@
         <v>179.0</v>
       </c>
       <c r="B180" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C180" s="35" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D180" s="35" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E180" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="181">
@@ -9172,16 +9249,16 @@
         <v>180.0</v>
       </c>
       <c r="B181" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C181" s="35" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E181" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="182">
@@ -9189,16 +9266,16 @@
         <v>181.0</v>
       </c>
       <c r="B182" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C182" s="35" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E182" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="183">
@@ -9206,16 +9283,16 @@
         <v>182.0</v>
       </c>
       <c r="B183" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C183" s="35" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E183" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="184">
@@ -9223,16 +9300,16 @@
         <v>183.0</v>
       </c>
       <c r="B184" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C184" s="35" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="D184" s="35" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E184" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="185">
@@ -9240,16 +9317,16 @@
         <v>184.0</v>
       </c>
       <c r="B185" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C185" s="35" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D185" s="35" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E185" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="186">
@@ -9257,16 +9334,16 @@
         <v>185.0</v>
       </c>
       <c r="B186" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C186" s="35" t="s">
+        <v>604</v>
+      </c>
+      <c r="D186" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="D186" s="35" t="s">
-        <v>592</v>
-      </c>
       <c r="E186" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="187">
@@ -9274,16 +9351,16 @@
         <v>186.0</v>
       </c>
       <c r="B187" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C187" s="35" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E187" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="188">
@@ -9291,16 +9368,16 @@
         <v>187.0</v>
       </c>
       <c r="B188" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C188" s="35" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D188" s="35" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E188" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="189">
@@ -9308,16 +9385,16 @@
         <v>188.0</v>
       </c>
       <c r="B189" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C189" s="35" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D189" s="35" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E189" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="190">
@@ -9325,16 +9402,16 @@
         <v>189.0</v>
       </c>
       <c r="B190" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C190" s="35" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D190" s="35" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="E190" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="191">
@@ -9342,16 +9419,16 @@
         <v>190.0</v>
       </c>
       <c r="B191" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C191" s="35" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D191" s="35" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="E191" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="192">
@@ -9359,16 +9436,16 @@
         <v>191.0</v>
       </c>
       <c r="B192" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C192" s="35" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D192" s="35" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="E192" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="193">
@@ -9376,16 +9453,16 @@
         <v>192.0</v>
       </c>
       <c r="B193" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C193" s="35" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D193" s="35" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="E193" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194">
@@ -9393,16 +9470,16 @@
         <v>193.0</v>
       </c>
       <c r="B194" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C194" s="35" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D194" s="35" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E194" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="195">
@@ -9410,16 +9487,16 @@
         <v>194.0</v>
       </c>
       <c r="B195" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C195" s="35" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D195" s="35" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E195" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="196">
@@ -9427,16 +9504,16 @@
         <v>195.0</v>
       </c>
       <c r="B196" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="C196" s="35" t="s">
+        <v>620</v>
+      </c>
+      <c r="D196" s="35" t="s">
         <v>499</v>
       </c>
-      <c r="C196" s="35" t="s">
-        <v>614</v>
-      </c>
-      <c r="D196" s="35" t="s">
-        <v>493</v>
-      </c>
       <c r="E196" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="197">
@@ -9444,16 +9521,16 @@
         <v>196.0</v>
       </c>
       <c r="B197" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C197" s="35" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D197" s="35" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="E197" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="198">
@@ -9461,16 +9538,16 @@
         <v>197.0</v>
       </c>
       <c r="B198" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C198" s="35" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D198" s="35" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="E198" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="199">
@@ -9478,16 +9555,16 @@
         <v>198.0</v>
       </c>
       <c r="B199" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C199" s="35" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D199" s="35" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="E199" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="200">
@@ -9495,16 +9572,16 @@
         <v>199.0</v>
       </c>
       <c r="B200" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C200" s="35" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D200" s="35" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="E200" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="201">
@@ -9512,16 +9589,16 @@
         <v>200.0</v>
       </c>
       <c r="B201" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C201" s="35" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D201" s="35" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="E201" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="202">
@@ -9529,16 +9606,16 @@
         <v>201.0</v>
       </c>
       <c r="B202" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C202" s="35" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D202" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E202" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="203">
@@ -9546,16 +9623,16 @@
         <v>202.0</v>
       </c>
       <c r="B203" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D203" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E203" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="204">
@@ -9563,16 +9640,16 @@
         <v>203.0</v>
       </c>
       <c r="B204" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C204" s="35" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D204" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E204" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="205">
@@ -9580,16 +9657,16 @@
         <v>204.0</v>
       </c>
       <c r="B205" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C205" s="35" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D205" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E205" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="206">
@@ -9597,16 +9674,16 @@
         <v>205.0</v>
       </c>
       <c r="B206" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C206" s="35" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D206" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E206" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="207">
@@ -9614,16 +9691,16 @@
         <v>206.0</v>
       </c>
       <c r="B207" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C207" s="35" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D207" s="35" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E207" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="208">
@@ -9631,16 +9708,16 @@
         <v>207.0</v>
       </c>
       <c r="B208" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C208" s="35" t="s">
+        <v>638</v>
+      </c>
+      <c r="D208" s="35" t="s">
         <v>632</v>
       </c>
-      <c r="D208" s="35" t="s">
-        <v>626</v>
-      </c>
       <c r="E208" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="209">
@@ -9648,16 +9725,16 @@
         <v>208.0</v>
       </c>
       <c r="B209" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C209" s="35" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D209" s="35" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E209" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="210">
@@ -9665,16 +9742,16 @@
         <v>209.0</v>
       </c>
       <c r="B210" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C210" s="35" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D210" s="35">
         <v>26.2</v>
       </c>
       <c r="E210" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="211">
@@ -9682,16 +9759,16 @@
         <v>210.0</v>
       </c>
       <c r="B211" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C211" s="35" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D211" s="35" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E211" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="212">
@@ -9699,16 +9776,16 @@
         <v>211.0</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D212" s="35" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="E212" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213">
@@ -9716,16 +9793,16 @@
         <v>212.0</v>
       </c>
       <c r="B213" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C213" s="35" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D213" s="35" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="E213" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="214">
@@ -9733,16 +9810,16 @@
         <v>213.0</v>
       </c>
       <c r="B214" s="35" t="s">
+        <v>505</v>
+      </c>
+      <c r="C214" s="35" t="s">
+        <v>647</v>
+      </c>
+      <c r="D214" s="35" t="s">
         <v>499</v>
       </c>
-      <c r="C214" s="35" t="s">
-        <v>641</v>
-      </c>
-      <c r="D214" s="35" t="s">
-        <v>493</v>
-      </c>
       <c r="E214" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="215">
@@ -9750,16 +9827,16 @@
         <v>214.0</v>
       </c>
       <c r="B215" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C215" s="35" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D215" s="35" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E215" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="216">
@@ -9767,16 +9844,16 @@
         <v>215.0</v>
       </c>
       <c r="B216" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C216" s="35" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D216" s="35" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E216" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="217">
@@ -9784,16 +9861,16 @@
         <v>216.0</v>
       </c>
       <c r="B217" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C217" s="35" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D217" s="35" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="E217" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="218">
@@ -9801,16 +9878,16 @@
         <v>217.0</v>
       </c>
       <c r="B218" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C218" s="35" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D218" s="35" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E218" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="219">
@@ -9818,16 +9895,16 @@
         <v>218.0</v>
       </c>
       <c r="B219" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C219" s="35" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D219" s="35" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E219" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="220">
@@ -9835,16 +9912,16 @@
         <v>219.0</v>
       </c>
       <c r="B220" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C220" s="35" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="D220" s="35" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="E220" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221">
@@ -9852,16 +9929,16 @@
         <v>220.0</v>
       </c>
       <c r="B221" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C221" s="35" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D221" s="35" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="E221" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222">
@@ -9869,16 +9946,16 @@
         <v>221.0</v>
       </c>
       <c r="B222" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C222" s="35" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D222" s="35" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E222" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="223">
@@ -9886,16 +9963,16 @@
         <v>222.0</v>
       </c>
       <c r="B223" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C223" s="35" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D223" s="35" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="E223" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224">
@@ -9903,16 +9980,16 @@
         <v>223.0</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E224" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225">
@@ -9920,16 +9997,16 @@
         <v>224.0</v>
       </c>
       <c r="B225" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C225" s="35" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D225" s="35" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E225" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226">
@@ -9937,16 +10014,16 @@
         <v>225.0</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D226" s="35">
         <v>3.0</v>
       </c>
       <c r="E226" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227">
@@ -9954,16 +10031,16 @@
         <v>226.0</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D227" s="35" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E227" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228">
@@ -9971,16 +10048,16 @@
         <v>227.0</v>
       </c>
       <c r="B228" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C228" s="35" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D228" s="35" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="E228" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="229">
@@ -9988,16 +10065,16 @@
         <v>228.0</v>
       </c>
       <c r="B229" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C229" s="35" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D229" s="35" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="E229" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="230">
@@ -10005,16 +10082,16 @@
         <v>229.0</v>
       </c>
       <c r="B230" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C230" s="35" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D230" s="35" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="E230" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="231">
@@ -10022,16 +10099,16 @@
         <v>230.0</v>
       </c>
       <c r="B231" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C231" s="35" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D231" s="35" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="E231" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="232">
@@ -10039,16 +10116,16 @@
         <v>231.0</v>
       </c>
       <c r="B232" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C232" s="35" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D232" s="35" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="E232" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="233">
@@ -10056,16 +10133,16 @@
         <v>232.0</v>
       </c>
       <c r="B233" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C233" s="35" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D233" s="35" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E233" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="234">
@@ -10073,16 +10150,16 @@
         <v>233.0</v>
       </c>
       <c r="B234" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C234" s="35" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D234" s="35" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E234" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="235">
@@ -10090,16 +10167,16 @@
         <v>234.0</v>
       </c>
       <c r="B235" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C235" s="35" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D235" s="35" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E235" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="236">
@@ -10107,16 +10184,16 @@
         <v>235.0</v>
       </c>
       <c r="B236" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C236" s="35" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D236" s="35" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="E236" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="237">
@@ -10124,16 +10201,16 @@
         <v>236.0</v>
       </c>
       <c r="B237" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C237" s="35" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D237" s="35" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="E237" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="238">
@@ -10141,16 +10218,16 @@
         <v>237.0</v>
       </c>
       <c r="B238" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C238" s="35" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="D238" s="35" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="E238" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="239">
@@ -10158,16 +10235,16 @@
         <v>238.0</v>
       </c>
       <c r="B239" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C239" s="35" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D239" s="35" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E239" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="240">
@@ -10175,16 +10252,16 @@
         <v>239.0</v>
       </c>
       <c r="B240" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C240" s="35" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="D240" s="35" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E240" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="241">
@@ -10192,16 +10269,16 @@
         <v>240.0</v>
       </c>
       <c r="B241" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C241" s="35" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="D241" s="35" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E241" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="242">
@@ -10209,16 +10286,16 @@
         <v>241.0</v>
       </c>
       <c r="B242" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C242" s="35" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D242" s="35" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E242" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243">
@@ -10226,16 +10303,16 @@
         <v>242.0</v>
       </c>
       <c r="B243" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C243" s="35" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="D243" s="35" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="E243" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244">
@@ -10243,16 +10320,16 @@
         <v>243.0</v>
       </c>
       <c r="B244" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C244" s="35" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D244" s="35" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="E244" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="245">
@@ -10260,16 +10337,16 @@
         <v>244.0</v>
       </c>
       <c r="B245" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C245" s="35" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D245" s="35" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="E245" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="246">
@@ -10277,16 +10354,16 @@
         <v>245.0</v>
       </c>
       <c r="B246" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C246" s="35" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="D246" s="35" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="E246" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247">
@@ -10294,16 +10371,16 @@
         <v>246.0</v>
       </c>
       <c r="B247" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C247" s="35" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D247" s="35" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="E247" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="248">
@@ -10311,16 +10388,16 @@
         <v>247.0</v>
       </c>
       <c r="B248" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C248" s="35" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="D248" s="35" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="E248" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="249">
@@ -10328,16 +10405,16 @@
         <v>248.0</v>
       </c>
       <c r="B249" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C249" s="35" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D249" s="35" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E249" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="250">
@@ -10345,16 +10422,16 @@
         <v>249.0</v>
       </c>
       <c r="B250" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C250" s="35" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="E250" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251">
@@ -10362,16 +10439,16 @@
         <v>250.0</v>
       </c>
       <c r="B251" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C251" s="35" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D251" s="35" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E251" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="252">
@@ -10379,16 +10456,16 @@
         <v>251.0</v>
       </c>
       <c r="B252" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C252" s="35" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="D252" s="35" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="E252" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253">
@@ -10396,16 +10473,16 @@
         <v>252.0</v>
       </c>
       <c r="B253" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C253" s="35" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D253" s="35" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E253" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254">
@@ -10413,16 +10490,16 @@
         <v>253.0</v>
       </c>
       <c r="B254" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C254" s="35" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="D254" s="35">
         <v>2026.2</v>
       </c>
       <c r="E254" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255">
@@ -10430,16 +10507,16 @@
         <v>254.0</v>
       </c>
       <c r="B255" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C255" s="35" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D255" s="35" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="E255" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="256">
@@ -10447,16 +10524,16 @@
         <v>255.0</v>
       </c>
       <c r="B256" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C256" s="35" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D256" s="35" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="E256" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="257">
@@ -10464,16 +10541,16 @@
         <v>256.0</v>
       </c>
       <c r="B257" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C257" s="35" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="D257" s="35" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E257" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="258">
@@ -10481,16 +10558,16 @@
         <v>257.0</v>
       </c>
       <c r="B258" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C258" s="35" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="D258" s="35" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="E258" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="259">
@@ -10498,16 +10575,16 @@
         <v>258.0</v>
       </c>
       <c r="B259" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C259" s="35" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D259" s="35" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E259" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="260">
@@ -10515,16 +10592,16 @@
         <v>259.0</v>
       </c>
       <c r="B260" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C260" s="35" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="D260" s="35" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="E260" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="261">
@@ -10532,16 +10609,16 @@
         <v>260.0</v>
       </c>
       <c r="B261" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C261" s="35" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D261" s="35" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="E261" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="262">
@@ -10549,19 +10626,22 @@
         <v>261.0</v>
       </c>
       <c r="B262" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C262" s="35" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D262" s="35" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="E262" s="35" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1" horizontalCentered="1"/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
@@ -10582,308 +10662,308 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="106" t="str">
+      <c r="A1" s="107" t="str">
         <f>'Project Team'!A1</f>
         <v>Last Name</v>
       </c>
-      <c r="B1" s="106" t="str">
+      <c r="B1" s="107" t="str">
         <f>'Project Team'!B1</f>
         <v>First Name</v>
       </c>
-      <c r="C1" s="107" t="s">
-        <v>729</v>
-      </c>
-      <c r="D1" s="108"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
+      <c r="C1" s="108" t="s">
+        <v>735</v>
+      </c>
+      <c r="D1" s="109"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
     </row>
     <row r="2">
-      <c r="A2" s="112" t="str">
+      <c r="A2" s="113" t="str">
         <f>'Project Team'!A2</f>
         <v>Fatima</v>
       </c>
-      <c r="B2" s="112" t="str">
+      <c r="B2" s="113" t="str">
         <f>'Project Team'!B2</f>
         <v>Qiblataina</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115" t="str">
+      <c r="C2" s="114"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="116" t="str">
         <f>average(C2:C10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F2" s="116" t="str">
+      <c r="F2" s="117" t="str">
         <f>if(stdev(C2:C7) &gt; 0,"NOK", "OK")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
     </row>
     <row r="3">
-      <c r="A3" s="118" t="str">
+      <c r="A3" s="119" t="str">
         <f>'Project Team'!A3</f>
         <v>Huy</v>
       </c>
-      <c r="B3" s="118" t="str">
+      <c r="B3" s="119" t="str">
         <f>'Project Team'!B3</f>
         <v>Christoph</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
     </row>
     <row r="4">
-      <c r="A4" s="112" t="str">
+      <c r="A4" s="113" t="str">
         <f>'Project Team'!A4</f>
         <v>Raza</v>
       </c>
-      <c r="B4" s="112" t="str">
+      <c r="B4" s="113" t="str">
         <f>'Project Team'!B4</f>
         <v>Asad</v>
       </c>
-      <c r="C4" s="113"/>
-      <c r="D4" s="114"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="115"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
     </row>
     <row r="5">
-      <c r="A5" s="118" t="str">
+      <c r="A5" s="119" t="str">
         <f>'Project Team'!A5</f>
         <v>Jokiel</v>
       </c>
-      <c r="B5" s="118" t="str">
+      <c r="B5" s="119" t="str">
         <f>'Project Team'!B5</f>
         <v>Rene</v>
       </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
     </row>
     <row r="6">
-      <c r="A6" s="112" t="str">
+      <c r="A6" s="113" t="str">
         <f>'Project Team'!A6</f>
         <v>Mosler</v>
       </c>
-      <c r="B6" s="112" t="str">
+      <c r="B6" s="113" t="str">
         <f>'Project Team'!B6</f>
         <v>Carl</v>
       </c>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="124">
+      <c r="C6" s="123"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="125">
         <v>0.0</v>
       </c>
-      <c r="F6" s="125" t="s">
-        <v>730</v>
-      </c>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
+      <c r="F6" s="126" t="s">
+        <v>736</v>
+      </c>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
     </row>
     <row r="7">
-      <c r="A7" s="118" t="str">
+      <c r="A7" s="119" t="str">
         <f>'Project Team'!A7</f>
         <v>Vineesh</v>
       </c>
-      <c r="B7" s="118" t="str">
+      <c r="B7" s="119" t="str">
         <f>'Project Team'!B7</f>
         <v>Koppay</v>
       </c>
-      <c r="C7" s="113"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="124">
+      <c r="C7" s="114"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="125">
         <v>1.0</v>
       </c>
-      <c r="F7" s="125" t="s">
-        <v>731</v>
-      </c>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
+      <c r="F7" s="126" t="s">
+        <v>737</v>
+      </c>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
     </row>
     <row r="8">
-      <c r="A8" s="112" t="str">
+      <c r="A8" s="113" t="str">
         <f>'Project Team'!A8</f>
         <v>Moeez</v>
       </c>
-      <c r="B8" s="112" t="str">
+      <c r="B8" s="113" t="str">
         <f>'Project Team'!B8</f>
         <v>Abdul</v>
       </c>
-      <c r="C8" s="113"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="124">
+      <c r="C8" s="114"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125">
         <v>2.0</v>
       </c>
-      <c r="F8" s="125" t="s">
-        <v>732</v>
-      </c>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
+      <c r="F8" s="126" t="s">
+        <v>738</v>
+      </c>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
     </row>
     <row r="9">
-      <c r="A9" s="118" t="str">
+      <c r="A9" s="119" t="str">
         <f>'Project Team'!A9</f>
         <v>Thakur</v>
       </c>
-      <c r="B9" s="118" t="str">
+      <c r="B9" s="119" t="str">
         <f>'Project Team'!B9</f>
         <v>Shikhar</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="124">
+      <c r="C9" s="114"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="125">
         <v>3.0</v>
       </c>
-      <c r="F9" s="125" t="s">
-        <v>733</v>
-      </c>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
+      <c r="F9" s="126" t="s">
+        <v>739</v>
+      </c>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
     </row>
     <row r="10">
-      <c r="A10" s="112" t="str">
+      <c r="A10" s="113" t="str">
         <f>'Project Team'!A10</f>
         <v>Dhruvin</v>
       </c>
-      <c r="B10" s="112" t="str">
+      <c r="B10" s="113" t="str">
         <f>'Project Team'!B10</f>
         <v>Vekariya</v>
       </c>
-      <c r="C10" s="113"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="124">
+      <c r="C10" s="114"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125">
         <v>5.0</v>
       </c>
-      <c r="F10" s="125" t="s">
-        <v>734</v>
-      </c>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
+      <c r="F10" s="126" t="s">
+        <v>740</v>
+      </c>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
     </row>
     <row r="11">
-      <c r="A11" s="126" t="s">
+      <c r="A11" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="113"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="124">
+      <c r="C11" s="114"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="125">
         <v>8.0</v>
       </c>
-      <c r="F11" s="125" t="s">
-        <v>735</v>
-      </c>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
+      <c r="F11" s="126" t="s">
+        <v>741</v>
+      </c>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
     </row>
     <row r="12">
-      <c r="A12" s="112"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="124">
+      <c r="A12" s="113"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="125">
         <v>13.0</v>
       </c>
-      <c r="F12" s="125" t="s">
-        <v>736</v>
-      </c>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
+      <c r="F12" s="126" t="s">
+        <v>742</v>
+      </c>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
     </row>
     <row r="13">
-      <c r="A13" s="118"/>
-      <c r="B13" s="118"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
+      <c r="A13" s="119"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
     </row>
     <row r="14">
-      <c r="A14" s="127" t="s">
-        <v>737</v>
-      </c>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
+      <c r="A14" s="128" t="s">
+        <v>743</v>
+      </c>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
     </row>
     <row r="15">
-      <c r="A15" s="129"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="129"/>
-      <c r="G15" s="129"/>
-      <c r="H15" s="129"/>
+      <c r="A15" s="130"/>
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="s">
-        <v>738</v>
-      </c>
-      <c r="B16" s="131"/>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
+      <c r="A16" s="131" t="s">
+        <v>744</v>
+      </c>
+      <c r="B16" s="132"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="s">
-        <v>739</v>
-      </c>
-      <c r="B17" s="129"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
+      <c r="A17" s="133" t="s">
+        <v>745</v>
+      </c>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="s">
-        <v>740</v>
-      </c>
-      <c r="B18" s="131"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="131"/>
+      <c r="A18" s="131" t="s">
+        <v>746</v>
+      </c>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
     </row>
     <row r="19">
-      <c r="A19" s="129"/>
-      <c r="B19" s="129"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
+      <c r="A19" s="130"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20">
-      <c r="A20" s="131"/>
-      <c r="B20" s="131"/>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131"/>
+      <c r="A20" s="132"/>
+      <c r="B20" s="132"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10916,10 +10996,10 @@
       </c>
       <c r="C1" s="4" t="str">
         <f>"Average Realized (" &amp; ROUND(AVERAGE(B2:B16), 0) &amp; " SP/s)"</f>
-        <v>Average Realized (25 SP/s)</v>
+        <v>Average Realized (28 SP/s)</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="F1" s="48" t="s">
         <v>174</v>
@@ -10942,8 +11022,8 @@
       <c r="L1" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="M1" s="133" t="s">
-        <v>742</v>
+      <c r="M1" s="134" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="2">
@@ -10954,9 +11034,9 @@
         <f>'Velocity Tracking'!B2</f>
         <v>1</v>
       </c>
-      <c r="C2" s="134">
+      <c r="C2" s="135">
         <f t="shared" ref="C2:C14" si="1">AVERAGE($B$2:$B$16)</f>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F2" s="52"/>
       <c r="G2" s="53"/>
@@ -10965,7 +11045,7 @@
       <c r="J2" s="54"/>
       <c r="K2" s="54"/>
       <c r="L2" s="54"/>
-      <c r="M2" s="135"/>
+      <c r="M2" s="136"/>
     </row>
     <row r="3">
       <c r="A3" s="43">
@@ -10976,9 +11056,9 @@
         <f>'Velocity Tracking'!B3</f>
         <v>12</v>
       </c>
-      <c r="C3" s="134">
+      <c r="C3" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F3" s="55" t="s">
         <v>181</v>
@@ -10989,7 +11069,7 @@
       <c r="J3" s="57"/>
       <c r="K3" s="57"/>
       <c r="L3" s="57"/>
-      <c r="M3" s="136"/>
+      <c r="M3" s="137"/>
     </row>
     <row r="4">
       <c r="A4" s="43">
@@ -11000,9 +11080,9 @@
         <f>'Velocity Tracking'!B4</f>
         <v>18</v>
       </c>
-      <c r="C4" s="134">
+      <c r="C4" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F4" s="52"/>
       <c r="G4" s="53"/>
@@ -11011,7 +11091,7 @@
       <c r="J4" s="54"/>
       <c r="K4" s="54"/>
       <c r="L4" s="54"/>
-      <c r="M4" s="135"/>
+      <c r="M4" s="136"/>
     </row>
     <row r="5">
       <c r="A5" s="43">
@@ -11022,9 +11102,9 @@
         <f>'Velocity Tracking'!B5</f>
         <v>36</v>
       </c>
-      <c r="C5" s="134">
+      <c r="C5" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F5" s="58" t="s">
         <v>182</v>
@@ -11041,7 +11121,7 @@
       </c>
       <c r="K5" s="30"/>
       <c r="L5" s="30"/>
-      <c r="M5" s="137">
+      <c r="M5" s="138">
         <f>I5/6</f>
         <v>20</v>
       </c>
@@ -11055,9 +11135,9 @@
         <f>'Velocity Tracking'!B6</f>
         <v>28</v>
       </c>
-      <c r="C6" s="134">
+      <c r="C6" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F6" s="52"/>
       <c r="G6" s="53"/>
@@ -11066,7 +11146,7 @@
       <c r="J6" s="54"/>
       <c r="K6" s="54"/>
       <c r="L6" s="54"/>
-      <c r="M6" s="135"/>
+      <c r="M6" s="136"/>
     </row>
     <row r="7">
       <c r="A7" s="43">
@@ -11077,9 +11157,9 @@
         <f>'Velocity Tracking'!B7</f>
         <v>21</v>
       </c>
-      <c r="C7" s="134">
+      <c r="C7" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F7" s="61" t="s">
         <v>183</v>
@@ -11090,7 +11170,7 @@
       <c r="J7" s="63"/>
       <c r="K7" s="63"/>
       <c r="L7" s="63"/>
-      <c r="M7" s="138"/>
+      <c r="M7" s="139"/>
     </row>
     <row r="8">
       <c r="A8" s="43">
@@ -11101,9 +11181,9 @@
         <f>'Velocity Tracking'!B8</f>
         <v>30</v>
       </c>
-      <c r="C8" s="134">
+      <c r="C8" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F8" s="64" t="s">
         <v>183</v>
@@ -11118,7 +11198,7 @@
       <c r="L8" s="65" t="s">
         <v>180</v>
       </c>
-      <c r="M8" s="139" t="str">
+      <c r="M8" s="140" t="str">
         <f>"Development Speed (≈" &amp; ROUND(M5, 0) &amp; " SP/s)"</f>
         <v>Development Speed (≈20 SP/s)</v>
       </c>
@@ -11132,9 +11212,9 @@
         <f>'Velocity Tracking'!B9</f>
         <v>18</v>
       </c>
-      <c r="C9" s="134">
+      <c r="C9" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F9" s="66">
         <v>1.0</v>
@@ -11157,7 +11237,7 @@
         <f>'Mid-Project Release plan'!G9</f>
         <v>120</v>
       </c>
-      <c r="M9" s="140">
+      <c r="M9" s="141">
         <f>$I$5</f>
         <v>120</v>
       </c>
@@ -11171,9 +11251,9 @@
         <f>'Velocity Tracking'!B10</f>
         <v>40</v>
       </c>
-      <c r="C10" s="134">
+      <c r="C10" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F10" s="52">
         <f t="shared" ref="F10:F11" si="3">F9+1</f>
@@ -11197,7 +11277,7 @@
         <f>'Mid-Project Release plan'!G10</f>
         <v>119</v>
       </c>
-      <c r="M10" s="140">
+      <c r="M10" s="141">
         <f t="shared" ref="M10:M15" si="4">M9-$M$5</f>
         <v>100</v>
       </c>
@@ -11211,9 +11291,9 @@
         <f>'Velocity Tracking'!B11</f>
         <v>33</v>
       </c>
-      <c r="C11" s="134">
+      <c r="C11" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F11" s="66">
         <f t="shared" si="3"/>
@@ -11237,7 +11317,7 @@
         <f>'Mid-Project Release plan'!G11</f>
         <v>107</v>
       </c>
-      <c r="M11" s="140">
+      <c r="M11" s="141">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
@@ -11251,9 +11331,9 @@
         <f>'Velocity Tracking'!B12</f>
         <v>32</v>
       </c>
-      <c r="C12" s="134">
+      <c r="C12" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F12" s="68">
         <v>4.0</v>
@@ -11276,7 +11356,7 @@
         <f>'Mid-Project Release plan'!G12</f>
         <v>89</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="141">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
@@ -11290,9 +11370,9 @@
         <f>'Velocity Tracking'!B13</f>
         <v>26</v>
       </c>
-      <c r="C13" s="134">
+      <c r="C13" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F13" s="70">
         <v>5.0</v>
@@ -11315,7 +11395,7 @@
         <f>'Mid-Project Release plan'!G13</f>
         <v>53</v>
       </c>
-      <c r="M13" s="140">
+      <c r="M13" s="141">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
@@ -11325,13 +11405,13 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B14" s="43" t="str">
+      <c r="B14" s="43">
         <f>'Velocity Tracking'!B14</f>
-        <v/>
-      </c>
-      <c r="C14" s="134">
+        <v>63</v>
+      </c>
+      <c r="C14" s="135">
         <f t="shared" si="1"/>
-        <v>24.58333333</v>
+        <v>27.53846154</v>
       </c>
       <c r="F14" s="71">
         <v>6.0</v>
@@ -11352,7 +11432,7 @@
         <f>'Mid-Project Release plan'!G14</f>
         <v>25</v>
       </c>
-      <c r="M14" s="140">
+      <c r="M14" s="141">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
@@ -11360,7 +11440,7 @@
     <row r="15">
       <c r="A15" s="43"/>
       <c r="B15" s="43"/>
-      <c r="C15" s="134"/>
+      <c r="C15" s="135"/>
       <c r="F15" s="43"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -11380,7 +11460,7 @@
         <f>'Mid-Project Release plan'!G15</f>
         <v/>
       </c>
-      <c r="M15" s="140">
+      <c r="M15" s="141">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -11388,11 +11468,11 @@
     <row r="16">
       <c r="A16" s="43"/>
       <c r="B16" s="43"/>
-      <c r="C16" s="134"/>
+      <c r="C16" s="135"/>
     </row>
     <row r="18">
       <c r="E18" s="35" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="F18" s="48" t="s">
         <v>174</v>
@@ -11415,8 +11495,8 @@
       <c r="L18" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="M18" s="133" t="s">
-        <v>742</v>
+      <c r="M18" s="134" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="19">
@@ -11427,7 +11507,7 @@
       <c r="J19" s="54"/>
       <c r="K19" s="54"/>
       <c r="L19" s="54"/>
-      <c r="M19" s="135"/>
+      <c r="M19" s="136"/>
     </row>
     <row r="20">
       <c r="F20" s="55" t="s">
@@ -11439,7 +11519,7 @@
       <c r="J20" s="57"/>
       <c r="K20" s="57"/>
       <c r="L20" s="57"/>
-      <c r="M20" s="136"/>
+      <c r="M20" s="137"/>
     </row>
     <row r="21">
       <c r="F21" s="52"/>
@@ -11449,7 +11529,7 @@
       <c r="J21" s="54"/>
       <c r="K21" s="54"/>
       <c r="L21" s="54"/>
-      <c r="M21" s="135"/>
+      <c r="M21" s="136"/>
     </row>
     <row r="22">
       <c r="F22" s="58" t="s">
@@ -11467,7 +11547,7 @@
       </c>
       <c r="K22" s="30"/>
       <c r="L22" s="30"/>
-      <c r="M22" s="137">
+      <c r="M22" s="138">
         <f>I22/7</f>
         <v>32.42857143</v>
       </c>
@@ -11480,7 +11560,7 @@
       <c r="J23" s="54"/>
       <c r="K23" s="54"/>
       <c r="L23" s="54"/>
-      <c r="M23" s="135"/>
+      <c r="M23" s="136"/>
     </row>
     <row r="24">
       <c r="F24" s="61" t="s">
@@ -11492,7 +11572,7 @@
       <c r="J24" s="63"/>
       <c r="K24" s="63"/>
       <c r="L24" s="63"/>
-      <c r="M24" s="138"/>
+      <c r="M24" s="139"/>
     </row>
     <row r="25">
       <c r="F25" s="52"/>
@@ -11505,7 +11585,7 @@
       <c r="L25" s="93" t="s">
         <v>180</v>
       </c>
-      <c r="M25" s="139" t="str">
+      <c r="M25" s="140" t="str">
         <f>"Development Speed (≈" &amp; ROUND(M22, 0) &amp; " SP/s)"</f>
         <v>Development Speed (≈32 SP/s)</v>
       </c>
@@ -11532,7 +11612,7 @@
         <f>'Final Project Release plan'!G9</f>
         <v>227</v>
       </c>
-      <c r="M26" s="140">
+      <c r="M26" s="141">
         <f>$I$22</f>
         <v>227</v>
       </c>
@@ -11560,7 +11640,7 @@
         <f>'Final Project Release plan'!G10</f>
         <v>197</v>
       </c>
-      <c r="M27" s="141">
+      <c r="M27" s="142">
         <f t="shared" ref="M27:M32" si="6">M26-$M$22</f>
         <v>194.5714286</v>
       </c>
@@ -11588,7 +11668,7 @@
         <f>'Final Project Release plan'!G11</f>
         <v>179</v>
       </c>
-      <c r="M28" s="141">
+      <c r="M28" s="142">
         <f t="shared" si="6"/>
         <v>162.1428571</v>
       </c>
@@ -11615,7 +11695,7 @@
         <f>'Final Project Release plan'!G12</f>
         <v>139</v>
       </c>
-      <c r="M29" s="141">
+      <c r="M29" s="142">
         <f t="shared" si="6"/>
         <v>129.7142857</v>
       </c>
@@ -11642,7 +11722,7 @@
         <f>'Final Project Release plan'!G13</f>
         <v>106</v>
       </c>
-      <c r="M30" s="141">
+      <c r="M30" s="142">
         <f t="shared" si="6"/>
         <v>97.28571429</v>
       </c>
@@ -11669,7 +11749,7 @@
         <f>'Final Project Release plan'!G14</f>
         <v>74</v>
       </c>
-      <c r="M31" s="141">
+      <c r="M31" s="142">
         <f t="shared" si="6"/>
         <v>64.85714286</v>
       </c>
@@ -11690,13 +11770,13 @@
       </c>
       <c r="K32" s="60">
         <f>'Final Project Release plan'!F15</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L32" s="60">
         <f>'Final Project Release plan'!G15</f>
         <v>48</v>
       </c>
-      <c r="M32" s="141">
+      <c r="M32" s="142">
         <f t="shared" si="6"/>
         <v>32.42857143</v>
       </c>
@@ -11706,7 +11786,7 @@
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
       <c r="L33" s="67"/>
-      <c r="M33" s="141"/>
+      <c r="M33" s="142"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -11738,16 +11818,16 @@
         <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>76</v>
@@ -11758,19 +11838,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
     <row r="3">
@@ -11778,19 +11858,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="4">
@@ -11798,19 +11878,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5">
@@ -11818,19 +11898,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="6">
@@ -11838,19 +11918,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>747</v>
-      </c>
       <c r="F6" s="35" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -11858,19 +11938,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -11878,19 +11958,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="9">
@@ -11898,19 +11978,19 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10">
@@ -11918,19 +11998,19 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11">
@@ -11938,19 +12018,19 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="12">
@@ -11958,19 +12038,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C12" s="142" t="s">
-        <v>645</v>
-      </c>
-      <c r="D12" s="142" t="s">
-        <v>766</v>
-      </c>
-      <c r="E12" s="142" t="s">
-        <v>453</v>
-      </c>
-      <c r="F12" s="142" t="s">
-        <v>767</v>
+        <v>505</v>
+      </c>
+      <c r="C12" s="143" t="s">
+        <v>651</v>
+      </c>
+      <c r="D12" s="143" t="s">
+        <v>772</v>
+      </c>
+      <c r="E12" s="143" t="s">
+        <v>459</v>
+      </c>
+      <c r="F12" s="143" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="13">
@@ -11978,19 +12058,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C13" s="142" t="s">
-        <v>768</v>
-      </c>
-      <c r="D13" s="142" t="s">
-        <v>769</v>
+        <v>505</v>
+      </c>
+      <c r="C13" s="143" t="s">
+        <v>774</v>
+      </c>
+      <c r="D13" s="143" t="s">
+        <v>775</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F13" s="142" t="s">
-        <v>770</v>
+        <v>322</v>
+      </c>
+      <c r="F13" s="143" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="14">
@@ -11998,19 +12078,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C14" s="142" t="s">
-        <v>625</v>
-      </c>
-      <c r="D14" s="142" t="s">
-        <v>771</v>
+        <v>505</v>
+      </c>
+      <c r="C14" s="143" t="s">
+        <v>631</v>
+      </c>
+      <c r="D14" s="143" t="s">
+        <v>777</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F14" s="142" t="s">
-        <v>772</v>
+        <v>322</v>
+      </c>
+      <c r="F14" s="143" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="15">
@@ -12018,19 +12098,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C15" s="142" t="s">
-        <v>632</v>
-      </c>
-      <c r="D15" s="142" t="s">
-        <v>771</v>
+        <v>505</v>
+      </c>
+      <c r="C15" s="143" t="s">
+        <v>638</v>
+      </c>
+      <c r="D15" s="143" t="s">
+        <v>777</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F15" s="142" t="s">
-        <v>773</v>
+        <v>322</v>
+      </c>
+      <c r="F15" s="143" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="16">
@@ -12038,19 +12118,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
     </row>
     <row r="17">
@@ -12058,19 +12138,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="18">
@@ -12078,19 +12158,19 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
     </row>
     <row r="19">
@@ -12098,19 +12178,19 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20">
@@ -12118,19 +12198,19 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21">
@@ -12138,19 +12218,19 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
     </row>
     <row r="22">
@@ -12158,19 +12238,19 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23">
@@ -12178,19 +12258,19 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
     </row>
     <row r="24">
@@ -12198,19 +12278,19 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
     </row>
     <row r="25">
@@ -12218,19 +12298,19 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
     <row r="26">
@@ -12238,19 +12318,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
     </row>
     <row r="27">
@@ -12258,19 +12338,19 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28">
@@ -12278,19 +12358,19 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
     </row>
     <row r="29">
@@ -12298,19 +12378,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="E29" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
     </row>
     <row r="30">
@@ -12318,19 +12398,19 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="E30" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="31">
@@ -12338,19 +12418,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="35" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
     </row>
     <row r="32">
@@ -14928,9 +15008,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B14" s="43" t="str">
+      <c r="B14" s="43">
         <f>IF('Final Project Release plan'!F15=0, "", 'Final Project Release plan'!F15)</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="C14" s="43">
         <f>IF(OR('Final Project Release plan'!D15=0, B13=""), "", 'Final Project Release plan'!D15)</f>
